--- a/artfynd/A 24220-2025 artfynd.xlsx
+++ b/artfynd/A 24220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126319836</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24220-2025 artfynd.xlsx
+++ b/artfynd/A 24220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126319836</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24220-2025 artfynd.xlsx
+++ b/artfynd/A 24220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126319836</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24220-2025 artfynd.xlsx
+++ b/artfynd/A 24220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,332 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126536880</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>442534</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6733769</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126536864</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442535</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6733770</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126537087</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80112</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>442517</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6733787</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24220-2025 artfynd.xlsx
+++ b/artfynd/A 24220-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126536880</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126536864</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126537087</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
